--- a/src/tablescan_local/default_templates/staircase.xlsx
+++ b/src/tablescan_local/default_templates/staircase.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staircase" sheetId="1" r:id="Ra08cd465f5e4417d"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Staircase" sheetId="1" ns1:id="R28baae5e99e04f9a"/>
+  </sheets>
+</workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -285,7 +285,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="15">
     <x:border/>
     <x:border>
       <x:bottom style="thin">
@@ -306,11 +306,75 @@
         <x:color rgb="FF333333"/>
       </x:bottom>
     </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none"/>
+      <x:top style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:top style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="none"/>
+      <x:top style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none"/>
+      <x:bottom style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:bottom style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="none"/>
+      <x:bottom style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -357,6 +421,19 @@
     <x:xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -371,31 +448,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Animals_staircase" displayName="Animals_staircase" ref="A6:R26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <tableColumns count="18">
-    <tableColumn id="1" name="ID">
-      <calculatedColumnFormula>ROW()-6</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" name="L1"/>
-    <tableColumn id="3" name="L2"/>
-    <tableColumn id="4" name="L3"/>
-    <tableColumn id="5" name="L4"/>
-    <tableColumn id="6" name="L5"/>
-    <tableColumn id="7" name="L6"/>
-    <tableColumn id="8" name="L7"/>
-    <tableColumn id="9" name="L drop"/>
-    <tableColumn id="10" name="R1"/>
-    <tableColumn id="11" name="R2"/>
-    <tableColumn id="12" name="R3"/>
-    <tableColumn id="13" name="R4"/>
-    <tableColumn id="14" name="R5"/>
-    <tableColumn id="15" name="R6"/>
-    <tableColumn id="16" name="R7"/>
-    <tableColumn id="17" name="R drop"/>
-    <tableColumn id="18" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Animals_staircase" displayName="Animals_staircase" ref="A6:R26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="18">
+    <x:tableColumn id="1" name="ID">
+      <x:calculatedColumnFormula>ROW()-6</x:calculatedColumnFormula>
+    </x:tableColumn>
+    <x:tableColumn id="2" name="L1"/>
+    <x:tableColumn id="3" name="L2"/>
+    <x:tableColumn id="4" name="L3"/>
+    <x:tableColumn id="5" name="L4"/>
+    <x:tableColumn id="6" name="L5"/>
+    <x:tableColumn id="7" name="L6"/>
+    <x:tableColumn id="8" name="L7"/>
+    <x:tableColumn id="9" name="L drop"/>
+    <x:tableColumn id="10" name="R1"/>
+    <x:tableColumn id="11" name="R2"/>
+    <x:tableColumn id="12" name="R3"/>
+    <x:tableColumn id="13" name="R4"/>
+    <x:tableColumn id="14" name="R5"/>
+    <x:tableColumn id="15" name="R6"/>
+    <x:tableColumn id="16" name="R7"/>
+    <x:tableColumn id="17" name="R drop"/>
+    <x:tableColumn id="18" name="Notes"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -652,7 +729,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1" autoPageBreaks="0"/>
   </sheetPr>
@@ -721,50 +798,50 @@
       <c r="R2" s="1"/>
     </row>
     <row r="3" ht="13" customHeight="1">
-      <c r="A3" s="3" t="str">
+      <c r="A3" s="27" t="str">
         <v>Date</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="3" t="str">
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="27" t="str">
         <v>Session</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="3" t="str">
+      <c r="E3" s="28"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="27" t="str">
         <v>Operator</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="29"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="32"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
     </row>
     <row r="5" ht="8" customHeight="1">
       <c r="A5" s="1"/>
@@ -1309,16 +1386,16 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G3:R3"/>
-    <mergeCell ref="G4:R4"/>
+    <mergeCell ref="G3:L3"/>
+    <mergeCell ref="G4:L4"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <pageMargins left="0.3937" right="0.3937" top="0.3937" bottom="0.3937" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1" horizontalDpi="0" verticalDpi="0"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <headerFooter/>
-  <legacyDrawing r:id="Rde50bb368d784bb8"/>
+  <legacyDrawing ns1:id="R49e6ed87d5f14cd1"/>
   <tableParts count="1">
-    <tablePart r:id="R7e3cc2b1ddf34913"/>
+    <tablePart ns1:id="Rbcafb5b67b5943d8"/>
   </tableParts>
 </worksheet>
 </file>
--- a/src/tablescan_local/default_templates/staircase.xlsx
+++ b/src/tablescan_local/default_templates/staircase.xlsx
@@ -1389,9 +1389,9 @@
     <mergeCell ref="G3:L3"/>
     <mergeCell ref="G4:L4"/>
   </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <pageMargins left="0.3937" right="0.3937" top="0.3937" bottom="0.3937" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1" horizontalDpi="0" verticalDpi="0"/>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <headerFooter/>
   <legacyDrawing ns1:id="R49e6ed87d5f14cd1"/>
   <tableParts count="1">
